--- a/xls/circular_clamped_16_tri3_16.xlsx
+++ b/xls/circular_clamped_16_tri3_16.xlsx
@@ -482,13 +482,13 @@
         <v>4050</v>
       </c>
       <c r="I16">
-        <v>-2.0919219719909496</v>
+        <v>-2.0919219718993283</v>
       </c>
       <c r="J16">
-        <v>-1.8948670558767664</v>
+        <v>-1.894867055900717</v>
       </c>
       <c r="K16">
-        <v>-1.0974334664554246</v>
+        <v>-1.0974334664574386</v>
       </c>
     </row>
   </sheetData>

--- a/xls/circular_clamped_16_tri3_16.xlsx
+++ b/xls/circular_clamped_16_tri3_16.xlsx
@@ -482,13 +482,13 @@
         <v>4050</v>
       </c>
       <c r="I16">
-        <v>-2.0919219718993283</v>
+        <v>-2.0919219719909496</v>
       </c>
       <c r="J16">
-        <v>-1.894867055900717</v>
+        <v>-1.8948670558767664</v>
       </c>
       <c r="K16">
-        <v>-1.0974334664574386</v>
+        <v>-1.0974334664554246</v>
       </c>
     </row>
   </sheetData>
